--- a/output/Tables/7000 steps/HIA_Rubin_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_Rubin_7000steps_1000replicate.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>158925.985</v>
+        <v>167169.431</v>
       </c>
       <c r="C2">
-        <v>153687.073</v>
+        <v>161732.393</v>
       </c>
       <c r="D2">
-        <v>164164.896</v>
+        <v>172606.47</v>
       </c>
       <c r="E2">
-        <v>1652131.035</v>
+        <v>1638309.899</v>
       </c>
       <c r="F2">
-        <v>1626266.279</v>
+        <v>1613004.869</v>
       </c>
       <c r="G2">
-        <v>1677995.791</v>
+        <v>1663614.928</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>219733427685.75</v>
+        <v>217895216510.584</v>
       </c>
       <c r="L2">
-        <v>216293415147.527</v>
+        <v>214529647548.064</v>
       </c>
       <c r="M2">
-        <v>223173440223.973</v>
+        <v>221260785473.104</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>145871.39</v>
+        <v>133609.452</v>
       </c>
       <c r="C3">
-        <v>142447.672</v>
+        <v>130513.595</v>
       </c>
       <c r="D3">
-        <v>149295.107</v>
+        <v>136705.308</v>
       </c>
       <c r="E3">
-        <v>130657.695</v>
+        <v>181823.631</v>
       </c>
       <c r="F3">
-        <v>128065.535</v>
+        <v>178161.163</v>
       </c>
       <c r="G3">
-        <v>133249.855</v>
+        <v>185486.099</v>
       </c>
       <c r="H3">
-        <v>8125328140.898</v>
+        <v>7040550066.181</v>
       </c>
       <c r="I3">
-        <v>7934620243.926</v>
+        <v>6877413911.318</v>
       </c>
       <c r="J3">
-        <v>8316036037.871</v>
+        <v>7203686221.043</v>
       </c>
       <c r="K3">
-        <v>17377473417.888</v>
+        <v>24182542930.697</v>
       </c>
       <c r="L3">
-        <v>17032716111.265</v>
+        <v>23695434635.711</v>
       </c>
       <c r="M3">
-        <v>17722230724.511</v>
+        <v>24669651225.683</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>130167.178</v>
+        <v>29793.247</v>
       </c>
       <c r="C4">
-        <v>127330.074</v>
+        <v>29104.573</v>
       </c>
       <c r="D4">
-        <v>133004.282</v>
+        <v>30481.921</v>
       </c>
       <c r="E4">
-        <v>194071.391</v>
+        <v>13857.336</v>
       </c>
       <c r="F4">
-        <v>188480.674</v>
+        <v>13565.6</v>
       </c>
       <c r="G4">
-        <v>199662.108</v>
+        <v>14149.072</v>
       </c>
       <c r="H4">
-        <v>1927385403.679</v>
+        <v>873508209.9170001</v>
       </c>
       <c r="I4">
-        <v>1885376404.016</v>
+        <v>853316965.502</v>
       </c>
       <c r="J4">
-        <v>1969394403.342</v>
+        <v>893699454.332</v>
       </c>
       <c r="K4">
-        <v>25811495036.037</v>
+        <v>1843025682.486</v>
       </c>
       <c r="L4">
-        <v>25067929677.166</v>
+        <v>1804224769.463</v>
       </c>
       <c r="M4">
-        <v>26555060394.909</v>
+        <v>1881826595.509</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>27774.653</v>
+        <v>20459.89</v>
       </c>
       <c r="C5">
-        <v>27141.059</v>
+        <v>20073.992</v>
       </c>
       <c r="D5">
-        <v>28408.246</v>
+        <v>20845.789</v>
       </c>
       <c r="E5">
-        <v>54681.355</v>
+        <v>37570.278</v>
       </c>
       <c r="F5">
-        <v>53323.887</v>
+        <v>36823.647</v>
       </c>
       <c r="G5">
-        <v>56038.824</v>
+        <v>38316.909</v>
       </c>
       <c r="H5">
-        <v>2088681647.876</v>
+        <v>802048156.205</v>
       </c>
       <c r="I5">
-        <v>2041034769.519</v>
+        <v>786920555.461</v>
       </c>
       <c r="J5">
-        <v>2136328526.233</v>
+        <v>817175756.949</v>
       </c>
       <c r="K5">
-        <v>7272620272.29</v>
+        <v>4996846982.729</v>
       </c>
       <c r="L5">
-        <v>7092076909.454</v>
+        <v>4897545115.327</v>
       </c>
       <c r="M5">
-        <v>7453163635.125</v>
+        <v>5096148850.131</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>51065.517</v>
+        <v>48262.408</v>
       </c>
       <c r="C6">
-        <v>49167.272</v>
+        <v>46517.178</v>
       </c>
       <c r="D6">
-        <v>52963.763</v>
+        <v>50007.639</v>
       </c>
       <c r="E6">
-        <v>81802.06600000001</v>
+        <v>55225.292</v>
       </c>
       <c r="F6">
-        <v>79569.12699999999</v>
+        <v>53176.935</v>
       </c>
       <c r="G6">
-        <v>84035.00599999999</v>
+        <v>57273.649</v>
       </c>
       <c r="H6">
-        <v>859892247.196</v>
+        <v>803472575.975</v>
       </c>
       <c r="I6">
-        <v>827927690.704</v>
+        <v>774417973.961</v>
       </c>
       <c r="J6">
-        <v>891856803.688</v>
+        <v>832527177.988</v>
       </c>
       <c r="K6">
-        <v>10879674829.757</v>
+        <v>7344963854.78</v>
       </c>
       <c r="L6">
-        <v>10582693882.737</v>
+        <v>7072532377.645</v>
       </c>
       <c r="M6">
-        <v>11176655776.778</v>
+        <v>7617395331.914</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>511597.327</v>
+        <v>439873.149</v>
       </c>
       <c r="C7">
-        <v>503634.57</v>
+        <v>433835.291</v>
       </c>
       <c r="D7">
-        <v>519560.083</v>
+        <v>445911.007</v>
       </c>
       <c r="E7">
-        <v>164684.922</v>
+        <v>160647.99</v>
       </c>
       <c r="F7">
-        <v>160493.668</v>
+        <v>157043.277</v>
       </c>
       <c r="G7">
-        <v>168876.175</v>
+        <v>164252.703</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>21903094608.12</v>
+        <v>21366182644.562</v>
       </c>
       <c r="L7">
-        <v>21345657893.442</v>
+        <v>20886755852.509</v>
       </c>
       <c r="M7">
-        <v>22460531322.798</v>
+        <v>21845609436.616</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>866476.0649999999</v>
+        <v>671998.1459999999</v>
       </c>
       <c r="C8">
-        <v>849720.647</v>
+        <v>660044.629</v>
       </c>
       <c r="D8">
-        <v>883231.4809999999</v>
+        <v>683951.664</v>
       </c>
       <c r="E8">
-        <v>625897.429</v>
+        <v>449124.527</v>
       </c>
       <c r="F8">
-        <v>609932.8910000001</v>
+        <v>438770.622</v>
       </c>
       <c r="G8">
-        <v>641861.968</v>
+        <v>459478.4319999999</v>
       </c>
       <c r="H8">
-        <v>13001287439.649</v>
+        <v>9519579008.278</v>
       </c>
       <c r="I8">
-        <v>12688959108.165</v>
+        <v>9292069406.242001</v>
       </c>
       <c r="J8">
-        <v>13313615771.134</v>
+        <v>9747088610.312</v>
       </c>
       <c r="K8">
-        <v>83244358164.092</v>
+        <v>59733562095.254</v>
       </c>
       <c r="L8">
-        <v>81121074474.064</v>
+        <v>58356492750.655</v>
       </c>
       <c r="M8">
-        <v>85367641854.121</v>
+        <v>61110631439.853</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>1025402.05</v>
+        <v>839167.577</v>
       </c>
       <c r="C9">
-        <v>1003407.72</v>
+        <v>821777.022</v>
       </c>
       <c r="D9">
-        <v>1047396.377</v>
+        <v>856558.134</v>
       </c>
       <c r="E9">
-        <v>2278028.464</v>
+        <v>2087434.426</v>
       </c>
       <c r="F9">
-        <v>2236199.17</v>
+        <v>2051775.491</v>
       </c>
       <c r="G9">
-        <v>2319857.759</v>
+        <v>2123093.36</v>
       </c>
       <c r="H9">
-        <v>13001287439.649</v>
+        <v>9519579008.278</v>
       </c>
       <c r="I9">
-        <v>12688959108.165</v>
+        <v>9292069406.242001</v>
       </c>
       <c r="J9">
-        <v>13313615771.134</v>
+        <v>9747088610.312</v>
       </c>
       <c r="K9">
-        <v>302977785849.842</v>
+        <v>277628778605.838</v>
       </c>
       <c r="L9">
-        <v>297414489621.5911</v>
+        <v>272886140298.719</v>
       </c>
       <c r="M9">
-        <v>308541082078.094</v>
+        <v>282371416912.957</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/HIA_Rubin_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_Rubin_7000steps_1000replicate.xlsx
@@ -682,26 +682,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B8">
-        <v>671998.1459999999</v>
+        <v>232124.997</v>
       </c>
       <c r="C8">
-        <v>660044.629</v>
+        <v>226209.338</v>
       </c>
       <c r="D8">
-        <v>683951.664</v>
+        <v>238040.657</v>
       </c>
       <c r="E8">
-        <v>449124.527</v>
+        <v>288476.537</v>
       </c>
       <c r="F8">
-        <v>438770.622</v>
+        <v>281727.345</v>
       </c>
       <c r="G8">
-        <v>459478.4319999999</v>
+        <v>295225.7289999999</v>
       </c>
       <c r="H8">
         <v>9519579008.278</v>
@@ -713,13 +713,13 @@
         <v>9747088610.312</v>
       </c>
       <c r="K8">
-        <v>59733562095.254</v>
+        <v>38367379450.692</v>
       </c>
       <c r="L8">
-        <v>58356492750.655</v>
+        <v>37469736898.146</v>
       </c>
       <c r="M8">
-        <v>61110631439.853</v>
+        <v>39265022003.237</v>
       </c>
     </row>
     <row r="9">
